--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_015.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_015.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="165">
   <si>
     <t>Sezione</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Madre</t>
@@ -559,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.390625" customWidth="true" bestFit="true"/>
@@ -1401,19 +1407,19 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
@@ -1424,19 +1430,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
@@ -1447,19 +1453,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1470,19 +1476,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1493,19 +1499,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1516,19 +1522,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1539,19 +1545,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1562,19 +1568,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1585,19 +1591,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1608,19 +1614,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1631,19 +1637,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1654,19 +1660,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1677,19 +1683,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1700,19 +1706,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1723,19 +1729,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1746,19 +1752,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1769,19 +1775,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1792,19 +1798,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1815,19 +1821,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1838,19 +1844,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1861,19 +1867,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1884,19 +1890,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1907,19 +1913,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1930,19 +1936,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1953,7 +1959,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>103</v>
@@ -1962,7 +1968,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>104</v>
@@ -1976,7 +1982,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>105</v>
@@ -1985,7 +1991,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>106</v>
@@ -1999,19 +2005,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2022,19 +2028,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2045,19 +2051,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2068,19 +2074,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2091,19 +2097,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2114,19 +2120,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="C68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2137,19 +2143,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2160,19 +2166,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2183,19 +2189,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2206,19 +2212,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2229,19 +2235,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2252,19 +2258,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2275,19 +2281,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2298,19 +2304,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2321,19 +2327,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2344,19 +2350,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2367,19 +2373,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2390,19 +2396,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2413,19 +2419,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2436,19 +2442,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2459,19 +2465,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2482,19 +2488,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2505,19 +2511,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2528,19 +2534,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2551,19 +2557,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2574,19 +2580,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2597,19 +2603,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2620,19 +2626,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2643,19 +2649,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2666,7 +2672,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>103</v>
@@ -2675,7 +2681,7 @@
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>104</v>
@@ -2689,7 +2695,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>105</v>
@@ -2698,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>106</v>
@@ -2712,19 +2718,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2735,19 +2741,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2758,19 +2764,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2781,19 +2787,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2804,19 +2810,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2830,16 +2836,16 @@
         <v>111</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2850,16 +2856,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>116</v>
@@ -2873,7 +2879,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>117</v>
@@ -2882,7 +2888,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>118</v>
@@ -2896,7 +2902,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>119</v>
@@ -2905,7 +2911,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>120</v>
@@ -2919,7 +2925,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>121</v>
@@ -2928,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>122</v>
@@ -2942,7 +2948,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>123</v>
@@ -2951,7 +2957,7 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>124</v>
@@ -2965,7 +2971,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>125</v>
@@ -2974,10 +2980,10 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -2988,19 +2994,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3011,7 +3017,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>128</v>
@@ -3020,10 +3026,10 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3034,19 +3040,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3057,7 +3063,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>131</v>
@@ -3066,7 +3072,7 @@
         <v>28</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>132</v>
@@ -3080,7 +3086,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>133</v>
@@ -3089,7 +3095,7 @@
         <v>28</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>134</v>
@@ -3103,16 +3109,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>136</v>
@@ -3126,19 +3132,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3149,16 +3155,16 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>142</v>
@@ -3172,7 +3178,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>143</v>
@@ -3181,7 +3187,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>144</v>
@@ -3195,7 +3201,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>145</v>
@@ -3204,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>146</v>
@@ -3218,7 +3224,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>147</v>
@@ -3227,7 +3233,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>148</v>
@@ -3241,7 +3247,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>149</v>
@@ -3250,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>150</v>
@@ -3264,7 +3270,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>151</v>
@@ -3273,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>152</v>
@@ -3287,19 +3293,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3310,16 +3316,16 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>158</v>
@@ -3333,16 +3339,16 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>160</v>
@@ -3356,16 +3362,16 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>162</v>
@@ -3374,6 +3380,29 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" s="2" t="s">
         <v>19</v>
       </c>
     </row>
